--- a/StructureDefinition-Remiss-Dokument.xlsx
+++ b/StructureDefinition-Remiss-Dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Remiss-Dokument.xlsx
+++ b/StructureDefinition-Remiss-Dokument.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="110">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Remiss : Dokument).</t>
+    <t>Klassen Remiss håller information om den remiss som ligger till grund för svaret.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -260,6 +260,10 @@
     <t>Source attribute: remiss-id</t>
   </si>
   <si>
+    <t>Angivelse av identitetsbeteckning för remissen.
+Benämns även RID.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.remisstidpunkt</t>
   </si>
   <si>
@@ -270,6 +274,9 @@
     <t>Source attribute: remisstidpunkt</t>
   </si>
   <si>
+    <t>Angivelse av tidpunkt för när en viss remissversion skapades.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.versionsnummer</t>
   </si>
   <si>
@@ -280,6 +287,10 @@
     <t>Source attribute: versionsnummer</t>
   </si>
   <si>
+    <t>Angivelse av löpnummer för remissversion.
+Varje ny version av en remiss behåller ursprungligt remiss-id och kan därför refereras av övriga versioner av samma remiss.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.fragestallning</t>
   </si>
   <si>
@@ -290,6 +301,9 @@
     <t>Source attribute: frågeställning</t>
   </si>
   <si>
+    <t>Angivelse av remissens frågeställning.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.efterfragadTjanst</t>
   </si>
   <si>
@@ -300,16 +314,26 @@
     <t>Source attribute: efterfrågad tjänst</t>
   </si>
   <si>
+    <t>Kod för typ av tjänst som efterfrågas i remissen.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.kommentarFranBestallare</t>
   </si>
   <si>
     <t>Source attribute: kommentar från beställare</t>
   </si>
   <si>
+    <t>Kommentar på beställningen av laboratorieundersökningen.</t>
+  </si>
+  <si>
     <t>Remiss-Dokument.medicinskInformation</t>
   </si>
   <si>
     <t>Source attribute: medicinsk information</t>
+  </si>
+  <si>
+    <t>Medicinsk information som angetts i beställningen relaterad till laboratorieundersökningen.</t>
   </si>
   <si>
     <t>Remiss-Dokument.besvarar</t>
@@ -915,7 +939,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -983,10 +1007,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1009,13 +1033,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1066,7 +1090,7 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
@@ -1083,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1109,13 +1133,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1166,7 +1190,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
@@ -1183,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1209,13 +1233,13 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1266,7 +1290,7 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1283,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1309,13 +1333,13 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1366,7 +1390,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>73</v>
@@ -1383,10 +1407,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1409,13 +1433,13 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1466,7 +1490,7 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>73</v>
@@ -1483,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1509,13 +1533,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1566,7 +1590,7 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>73</v>
@@ -1583,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1609,13 +1633,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1666,7 +1690,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>73</v>
@@ -1683,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1709,13 +1733,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1766,7 +1790,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>73</v>
